--- a/MIL-STD-461C_ASC/DM_CM_PFC.xlsx
+++ b/MIL-STD-461C_ASC/DM_CM_PFC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\9108h\Documents\LTspice\MIL-STD-461C_ASC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A05E3A1-F667-4935-9764-FB1329D28DB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D391466-E295-4432-A7EF-BE14F86553D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="810" yWindow="45" windowWidth="25050" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -741,7 +741,8 @@
         <v>13</v>
       </c>
       <c r="F5" s="6">
-        <v>320</v>
+        <f>460*0.9</f>
+        <v>414</v>
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
@@ -780,7 +781,7 @@
       </c>
       <c r="F7" s="6">
         <f>F5/F6</f>
-        <v>355.55555555555554</v>
+        <v>460</v>
       </c>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
@@ -800,7 +801,7 @@
       </c>
       <c r="F8" s="6">
         <f>F4^2/F7</f>
-        <v>37.1953125</v>
+        <v>28.75</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
